--- a/docs/SOAL_1B_WBS_PROCUREMENT.xlsx
+++ b/docs/SOAL_1B_WBS_PROCUREMENT.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WBS Procurement System" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WBS Modul &amp; Fitur" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Matriks Hak Akses (RBAC)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Spesifikasi &amp; Scope" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +31,13 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="001E3A8A"/>
-      <sz val="15"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <i val="1"/>
       <color rgb="00475569"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -51,11 +53,57 @@
     </font>
     <font>
       <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="000F172A"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0094A3B8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -70,8 +118,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFF6FF"/>
-        <bgColor rgb="00EFF6FF"/>
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,13 +147,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001E3A8A"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -107,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -118,22 +198,73 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -501,22 +632,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>WORK BREAKDOWN STRUCTURE (WBS) - APLIKASI PENGADAAN BARANG &amp; JASA (PROCUREMENT)</t>
+          <t>WORK BREAKDOWN STRUCTURE (WBS) — SISTEM PENGADAAN BARANG &amp; JASA (PROCUREMENT)</t>
         </is>
       </c>
     </row>
@@ -536,7 +670,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Nama Modul / Fitur / Deliverable</t>
+          <t>Nama Modul / Fitur / Komponen Kerja</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -551,15 +685,30 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Peran Penanggung Jawab (Role)</t>
+          <t>Role Penanggung Jawab</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Keluaran (Deliverable / Output)</t>
+          <t>Source Code &amp; Berkas Acuan</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Fitur Unggulan / AI Assistant</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Keluaran (Deliverable Output)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Bobot (%)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Status Kesiapan</t>
         </is>
@@ -583,7 +732,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Sistem manajemen akses terpusat berbasis 5 hak akses peran (RBAC)</t>
+          <t>Sistem manajemen akses terpusat berbasis 5 hak akses peran (Role-Based Access Control)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -593,121 +742,181 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Sistem Login Aman &amp; Sesi Berbasis Cookie</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
+          <t>app.py, models.py, base.html</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Session Guard &amp; Cookie Security</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Sistem Login Terlindungi &amp; Middleware RBAC</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Selesai (100%)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Halaman Login &amp; Portal Terpadu</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Portal Login &amp; Halaman Masuk Terpadu</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Portal login dengan infografis alur pengadaan melingkar &amp; human check anti-bot</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>All Roles</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Form Autentikasi dengan CSRF &amp; Session Guard</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Halaman login dengan infografis alur sirkular interaktif 4-tahapan &amp; verifikasi anti-bot human check</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Semua Role</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>templates/auth/login.html, app.py:login()</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Circular Infographic &amp; Human Anti-Bot</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Form Autentikasi Modern Bebas Brute Force</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Selesai (100%)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Pemisahan Hak Akses (Role-Based Access Control)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Pemisahan Hak Akses Multi-Peran (RBAC)</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Proteksi endpoint @role_required untuk Requester, Approver, Purchasing, Warehouse, Admin</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Proteksi decorator @role_required untuk 5 roles: Requester, Approver, Purchasing, Warehouse, Admin</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>System Admin</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Middleware &amp; Decorator RBAC</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>app.py:role_required()</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Role-Based Endpoint Protection</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>Hak Akses Menu &amp; Routing Terisolasi Aman</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>Selesai (100%)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Manajemen Akun Pengguna &amp; Profil</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Manajemen Akun &amp; Modal Profil Pengguna</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Pengelolaan kredensial aman (PBKDF2 SHA256), modal edit profil, &amp; ganti password</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>All Roles</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Modal Profil Interaktif &amp; Database Users</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Pengelolaan kredensial terenkripsi (PBKDF2 SHA256), modal edit profil, nama, email &amp; ganti password</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Semua Role</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>templates/base.html, app.py:update_profile()</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Modal &amp; Password Encryptor</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Data Master Pengguna &amp; Audit Identitas</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>Selesai (100%)</t>
         </is>
@@ -731,7 +940,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Siklus awal identifikasi dan permohonan pengadaan barang/jasa</t>
+          <t>Siklus awal permohonan pengadaan barang/jasa dari divisi pemohon hingga submit dokumen</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -741,1159 +950,2251 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Dokumen Elektronik PR &amp; Item Relasional</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+          <t>app.py, models.py, templates/pr/*</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Dynamic Multi-Item Grid &amp; AI Catalog Scan</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Dokumen Elektronik PR &amp; Database Relasional</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>Selesai (100%)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Pengajuan Permohonan PR Baru</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Formulir Pengajuan Permohonan PR Baru</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Formulir interaktif dengan auto-generated nomor PR unik (PR/YYYY/MM/XXXX)</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Formulir interaktif dengan penomoran unik otomatis format resmi (PR/YYYY/MM/XXXX)</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Requester</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Nomor Registrasi PR &amp; Header Dokumen</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>templates/pr/create.html, app.py:pr_create()</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Auto-Generate Nomor Registrasi PR</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Header Dokumen Permohonan Pengadaan</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>Selesai (100%)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Multi-Item Grid Dinamis</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Grid Multi-Item Dinamis &amp; Live Calculator</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Tambah/hapus baris item kebutuhan tanpa refresh halaman, auto-kalkulasi subtotal &amp; grand total</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Tambah/hapus baris item kebutuhan tanpa reload, live calculation subtotal dan grand total anggaran</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Requester</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Tabel Rincian PR (Nama, Spek, Qty, Harga)</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>templates/pr/create.html, static/js/script.js</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Real-Time Subtotal &amp; Total Estimator</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>Tabel Item Kebutuhan (Spek, Qty, Harga)</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>Selesai (100%)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>AI Vision Smart Catalog Scanner (Fitur Nilai Plus)</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>AI Vision: Smart Catalog &amp; Brosur Scanner</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Ekstraksi OCR otomatis dari foto brosur/katalog barang langsung mengisi baris tabel PR</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Ekstraksi OCR otomatis dari foto brosur/katalog/nota toko langsung mengisi tabel baris item PR</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Requester</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Input Cepat Berbasis AI Vision</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>app.py:ai_scan_pr_catalog(), templates/pr/create.html</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>AI Computer Vision Scanner (Fitur Plus)</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Input Otomatis Multi-Item via AI Vision</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>Selesai (100%)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Monitoring Status &amp; Riwayat PR</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Template Cepat Kebutuhan (Quick Suggestion Tags)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Tabel filter pills (Semua, Menunggu, Disetujui, Ditolak, PO Terbit) dan pencarian real-time</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Preset satu-klik item pengadaan populer (Laptop ThinkPad, Monitor 4K, ATK PaperOne)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Requester</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Daftar Riwayat Pengajuan PR</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>templates/pr/create.html</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>One-Click Item Recommendation Chips</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>Efisiensi Input Form Permohonan</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>Selesai (100%)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Dokumen Resmi Pengajuan PR</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Monitoring Status PR &amp; Live Search Filters</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Halaman detail dokumen PR siap cetak dengan riwayat status &amp; catatan revisi</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Filter pills status (Semua, Menunggu, Disetujui, Ditolak, PO Terbit) dan pencarian instan</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Requester</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>templates/pr/list.html, app.py:pr_list()</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Filter Pills &amp; Live Client-side Search</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Daftar Riwayat Permohonan Terstruktur</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Slip Dokumen Resmi PR Siap Cetak (A4)</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Level 2 (Fitur)</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Detail dokumen PR dengan Kop Surat formal, rekam jejak status, dan tanda tangan pemohon</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Requester / Approver</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Slip Formal PR Standar A4</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>templates/pr/detail.html</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Kop Surat Formal &amp; Status Stampel</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Lembar Bukti Pengajuan PR Standar A4</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>MODUL OTORISASI &amp; APPROVAL WORKFLOW</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Level 1 (Modul)</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Mekanisme tata kelola dan persetujuan anggaran oleh pimpinan divisi</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Mekanisme tata kelola dan persetujuan anggaran pengadaan oleh pimpinan departemen</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Approver</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Keputusan Approval &amp; Audit Trail</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>app.py, models.py, templates/approval/*</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Priority Queue &amp; Real-Time Decision Audit</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Keputusan Otorisasi &amp; Log Audit Pimpinan</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Antrean PR Menunggu Persetujuan</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Antrean PR Prioritas Menunggu Otorisasi</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Dashboard antrean permohonan prioritas dengan badge urgensi tanggal kebutuhan</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Dashboard antrean permohonan PR dengan highlight tanggal kebutuhan dan indikator urgensi</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Approver</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Tabel Antrean Otorisasi Pimpinan</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>templates/approval/list.html, app.py:approval_list()</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Urgency Badge &amp; Priority Queue List</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>Daftar PR Menunggu Persetujuan Pimpinan</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Peninjauan Rincian Teknis &amp; Anggaran</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Pemeriksaan detail spesifikasi barang, kewajaran estimasi harga, dan total belanja</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Lembar evaluasi spesifikasi barang, kewajaran estimasi harga pasar, dan total pagu belanja</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Approver</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Lembar Evaluasi Pengadaan</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>templates/approval/review.html, app.py:approval_review()</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Comparative Price &amp; Specs Breakdown</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Review Objektif Dokumen Pengadaan</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Aksi Keputusan: Approve atau Reject</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Eksekusi Keputusan Otorisasi (Approve / Reject)</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Tombol eksekusi persetujuan atau penolakan wajib menyertakan catatan evaluasi pimpinan</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Tombol eksekusi otorisasi pimpinan wajib menyertakan catatan evaluasi atau alasan penolakan</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Approver</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Status Terverifikasi &amp; Log Tanggal Otorisasi</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>app.py:approval_action(), templates/approval/review.html</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>SweetAlert2 Confirmation &amp; Mandatory Notes</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>Status Approval Resmi &amp; Tanggal Otorisasi</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Notifikasi Real-Time Feedback</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Notifikasi Real-Time Feedback Status PR</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Alert status instan untuk memberi kejelasan status dokumen kepada Requester</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Notifikasi status instan kepada Requester bila pengajuan disetujui atau ditolak pimpinan</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Approver / Requester</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Banner Status Approval Interaktif</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>templates/base.html, app.py:flash()</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Flash Feedback &amp; Status Banner Alert</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Transparansi Alur Otorisasi Internal</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>MODUL PURCHASE ORDER (PO) &amp; REKANAN VENDOR</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Level 1 (Modul)</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Penerbitan surat pesanan resmi kepada vendor rekanan terpilih</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Penerbitan surat pesanan resmi kepada rekanan vendor berdasarkan PR yang telah disetujui</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Dokumen Kontrak PO &amp; Perjanjian Vendor</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>app.py, models.py, templates/po/*</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>AI Quotation OCR, Terms Sourcing &amp; Legal Print</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Dokumen Kontrak PO &amp; Perjanjian Legal Vendor</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Antrean PR Siap Terbit PO</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Antrean PR Siap Diterbitkan Menjadi PO</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Daftar permohonan yang telah disetujui (Approved) dan menunggu pemilihan vendor</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Daftar dokumen PR berstatus Approved yang siap diproses untuk penetapan rekanan vendor</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>Tabel Seleksi Pengadaan</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>templates/po/list.html, app.py:po_list()</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Auto-Sourcing Eligible PR Queue</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Daftar Seleksi PR Terotorisasi</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Penerbitan Kontrak PO Baru</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Formulir Penerbitan Kontrak PO Baru</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Formulir kontrak PO lengkap dengan Nomor PO otomatis (PO/YYYY/MM/XXXX)</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Formulir kontrak pesanan resmi dengan nomor registrasi unik otomatis (PO/YYYY/MM/XXXX)</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Dokumen PO Terbit</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>templates/po/create.html, app.py:po_create()</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Auto-Generate Nomor Kontrak PO</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>Header Dokumen Purchase Order</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>AI Vision Quotation Scanner (Fitur Nilai Plus)</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>AI Vision: Smart Vendor Quotation Scanner</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Ekstraksi OCR surat penawaran resmi vendor otomatis mengisi data vendor &amp; payment terms</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Ekstraksi OCR foto/scan surat penawaran resmi vendor otomatis mengisi data profil &amp; syarat bayar</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Input Form Rekanan Cepat via AI</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>app.py:ai_scan_vendor_quotation(), templates/po/create.html</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>AI Computer Vision Quotation (Fitur Plus)</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Pengisian Cepat Rekanan Vendor via AI</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Quick Auto-Fill Rekanan Terdaftar</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Quick Auto-Fill Rekanan Vendor Terdaftar</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Preset satu klik data rekanan terverifikasi (Solusi Mitra, ATK Berkah, Triputra Daya)</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Pilihan cepat rekanan resmi (PT Solusi Mitra Informatika, CV ATK Berkah, PT Triputra Daya)</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Pengisian Otomatis Profil Vendor</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>templates/po/create.html</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Vendor Profile Presets One-Click</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>Otomasi Input Identitas Rekanan</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Negosiasi Harga Deal Satuan</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Negosiasi Harga Deal &amp; Live Recalculate PO</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Penyesuaian harga final kesepakatan dengan live calculator subtotal &amp; grand total PO</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Penyesuaian harga deal satuan dengan kalkulasi otomatis subtotal dan total nilai kontrak PO</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Tabel Harga Kontrak Pesanan</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>templates/po/create.html, static/js/script.js</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Live Recalculate Subtotal &amp; Grand Total</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Tabel Harga Kesepakatan Final Pesanan</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Cetak Dokumen Resmi PO Standar A4</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Cetak Slip PO Legal Standar A4 Resmi</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Cetak slip PO formal lengkap dengan Kop Surat Perusahaan, Cap Stempel Digital, &amp; 3 Tanda Tangan</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Format cetak PO ber-Kop Surat Perusahaan, Cap Stempel Digital, &amp; 3 Kolom Tanda Tangan Legal</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Purchasing / Vendor</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Dokumen Legal PO Siap Kirim (PDF Print)</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>templates/po/detail.html, static/css/style.css</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Corporate Letterhead, Digital Stamp &amp; 3-Sign</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>Surat Pesanan Legal Siap Kirim ke Vendor</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>MODUL GOODS RECEIPT (GR) &amp; FISIK GUDANG</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Level 1 (Modul)</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Verifikasi penerimaan fisik barang dan surat jalan di gudang logistik</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Verifikasi penerimaan fisik barang dan surat jalan kurir di gudang (Titik Akhir Scope Pengadaan)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Surat Bukti Penerimaan Barang (GR Slip)</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>app.py, models.py, templates/gr/*</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>AI Delivery Order OCR &amp; Physical Tagging</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Berita Acara Penerimaan Barang (GR Slip)</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Antrean PO Menunggu Kedatangan Fisik</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Monitoring Kedatangan Fisik Kargo Logistik</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Monitoring Purchase Order berstatus aktif (Issued) yang belum diterima di gudang</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Pemantauan daftar PO berstatus aktif (Issued) yang sedang dalam pengiriman ekspedisi ke gudang</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Daftar Kedatangan Kargo Logistik</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>templates/gr/list.html, app.py:gr_list()</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Inbound Cargo Tracker &amp; PO Reference Card</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>Antrean Penerimaan Fisik Kargo</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>AI Computer Vision: Smart Scanner Surat Jalan (Fitur Nilai Plus)</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>AI Computer Vision: Smart Scanner Surat Jalan (DO)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Pemindaian dokumen Delivery Order (DO) fisik kurir untuk ekstraksi nomor DO &amp; kondisi segel</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Pemindaian dokumen Delivery Order (DO) kurir untuk ekstrak nomor DO, tanggal &amp; kondisi segel</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Input Data Surat Jalan Otomatis</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>app.py:ai_scan_delivery_order(), templates/gr/create.html</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>AI Computer Vision DO Scanner (Fitur Plus)</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Ekstraksi Otomatis Surat Jalan Vendor</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Pemeriksaan Kuantitas &amp; Kondisi Fisik</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Inspeksi Fisik: Cek Kuantitas &amp; Tagging Kondisi</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Verifikasi kuantitas riil per item serta tagging kondisi: Baik, Rusak, atau Salah Tipe</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Verifikasi kuantitas fisik riil vs PO serta penandaan kondisi fisik: Baik / Rusak / Salah Tipe</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Berita Acara Pemeriksaan Fisik</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>templates/gr/create.html, app.py:gr_create()</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Defect &amp; Damage Physical Tagging</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>Data Verifikasi Fisik Kargo Gudang</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Kalkulasi Otomatis Status Penerimaan</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Auto-Calculated Status Penerimaan PO</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>Sistem otomatis menetapkan status Received (Lengkap) atau Partially Received (Sebagian)</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Update Status PO &amp; GR Real-Time</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>app.py:gr_create(), models.py:PurchaseOrder</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Automated Partial / Full Status Evaluator</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Update Status PO &amp; GR Terintegrasi</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Cetak Lembar Tanda Terima Goods Receipt</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Cetak Slip Bukti Serah Terima Goods Receipt</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Pencetakan slip serah terima barang gudang resmi ber-Kop Surat dan tanda tangan penerima</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Pencetakan Berita Acara Penerimaan Barang standar A4 lengkap dengan Kop Surat &amp; Tanda Tangan</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Dokumen Fisik GR Berita Acara</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>templates/gr/detail.html, static/css/style.css</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Official Warehouse GR Slip &amp; Signature Area</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>Slip Legal Tanda Terima Fisik Barang</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>MODUL ANALITIK, DASHBOARD &amp; PELAPORAN</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Level 1 (Modul)</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Pusat informasi KPI dan rekapitulasi performa pengadaan organisasi</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>All Roles</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Laporan Manajemen &amp; Grafik Tren</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Pusat informasi metrik KPI, statistik pengadaan, grafik real-time, dan transparansi alur transaksi</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Semua Role</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>templates/dashboard/*, app.py:dashboard()</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Role-Tailored KPI Cards &amp; Chart.js Real-time</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Dasbor Eksekutif &amp; Ringkasan Performa</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Role-Tailored Dashboard Eksekutif</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Tampilan metrik statistik disesuaikan khusus untuk tiap peran yang sedang login</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>All Roles</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Dasbor Interaktif Khusus Role</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Metrik statistik disesuaikan khusus untuk tiap peran: Requester, Approver, Purchasing, Warehouse, Admin</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Semua Role</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>templates/dashboard/index.html</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Custom Dynamic Metrics per User Role</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>Panel Monitoring Khusus Masing-masing Role</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Visualisasi Grafik Real-Time (Chart.js)</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>Grafik distribusi status pengadaan dan tren belanja anggaran per divisi</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Grafik status pengadaan dan diagram batang tren realisasi belanja anggaran per departemen</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>Approver / Admin</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Widget Visual Tren Pengadaan</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>templates/dashboard/index.html, Chart.js</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Interactive Donut &amp; Bar Charts</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Visualisasi Tren Pengadaan Organisasi</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Audit Trail &amp; Rekap Riwayat Transaksi</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Audit Trail &amp; Pelacakan Alur Dokumen</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Pelacakan alur dokumen hulu-hilir (PR &amp;rarr; Approval &amp;rarr; PO &amp;rarr; GR) secara transparan</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Pelacakan hulu-ke-hilir siklus pengadaan (PR -&gt; Approval -&gt; PO -&gt; GR) secara transparan</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Admin / Auditor</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Log Aktivitas Lengkap Sistem</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>app.py, templates/dashboard/index.html</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>End-to-End Transaction Traceability</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>Log Riwayat Transaksi Lengkap</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>FITUR OPSIONAL NILAI PLUS: AI VISION SUITE</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Level 1 (Modul)</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Implementasi Computer Vision &amp; AI Model terpadu untuk efisiensi form input</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Penerapan Computer Vision &amp; AI Model terintegrasi di 3 titik proses pengadaan untuk seluruh role</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Cross-Role</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Suite Asisten AI Pengadaan Cerdas</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>app.py, templates/pr/*, templates/po/*, templates/gr/*</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Multi-Stage Computer Vision &amp; OCR Ecosystem</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Ekosistem AI Pengadaan Modern</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Nilai Plus</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>AI Smart Catalog Extractor (Requester)</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>AI Smart Catalog &amp; Brosur Scanner (Requester)</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Ekstraksi multi-item otomatis dari foto katalog/brosur ke form PR</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Ekstraksi multi-item otomatis dari foto brosur/katalog toko langsung mengisi tabel baris item PR</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Requester</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>Pengisian Otomatis Item PR via AI</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>app.py:ai_scan_pr_catalog(), templates/pr/create.html</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>AI Multi-Item Catalog Extractor</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>Otomasi Form PR Berbasis AI Vision</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>Nilai Plus</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>AI Quotation OCR Extractor (Purchasing)</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>AI Vendor Quotation Scanner (Purchasing)</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>Ekstraksi otomatis lembar surat penawaran vendor ke form PO</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Ekstraksi otomatis lembar surat penawaran rekanan vendor mengisi profil vendor &amp; payment terms PO</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Pengisian Otomatis Vendor PO via AI</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>app.py:ai_scan_vendor_quotation(), templates/po/create.html</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>AI Quotation OCR Extractor</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Otomasi Form PO Berbasis AI Vision</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Nilai Plus</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>AI Delivery Order Scanner (Warehouse)</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Level 2 (Fitur)</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Ekstraksi nomor DO &amp; deteksi kondisi segel fisik paket pengiriman</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>Ekstraksi nomor DO &amp; verifikasi kondisi fisik segel kemasan barang dari surat jalan kurir</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Pengisian Otomatis Form GR via AI</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>Selesai (100%)</t>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>app.py:ai_scan_delivery_order(), templates/gr/create.html</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>AI DO &amp; Packaging Integrity Checker</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>Otomasi Form GR Berbasis AI Vision</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>Nilai Plus</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>Selesai (100%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>MATRIKS HAK AKSES &amp; OTORITAS PENGGUNA (ROLE-BASED ACCESS CONTROL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Pemetaan 5 Peran: Requester, Approver, Purchasing, Warehouse, dan System Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="10" customHeight="1"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Modul &amp; Fungsi Sistem</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Requester (Pemohon)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Approver (Dept Head)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Purchasing (Sourcing)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Warehouse (Gudang)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>System Administrator</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Keterangan Kebijakan Tata Kelola</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Login Portal &amp; Autentikasi Human Check</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Bisa Akses</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Bisa Akses</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Bisa Akses</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Bisa Akses</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Bisa Akses</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Semua user wajib verifikasi kredensial</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Edit Profil Akun &amp; Ganti Password</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Bisa Akses</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Bisa Akses</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Bisa Akses</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Bisa Akses</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Bisa Akses</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>Setiap user mengelola kredensial sendiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Buat Purchase Requisition (PR Baru)</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>FULL AKSES (CREATE)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Hak eksklusif divisi pemohon barang</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>AI Smart Catalog &amp; Brosur Scanner</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>FULL AKSES (AI SCAN)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>Membantu ekstraksi barang di form PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Tinjau &amp; Otorisasi PR (Approve / Reject)</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>FULL AKSES (APPROVE)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>Kewenangan otorisasi pimpinan divisi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Terbitkan Purchase Order Resmi (PO)</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>FULL AKSES (CREATE)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>Hak negosiasi &amp; kontrak rekanan vendor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>AI Vendor Quotation OCR Scanner</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>FULL AKSES (AI SCAN)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Ekstraksi otomatis surat penawaran vendor</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Cetak Lembar PO Legal Standar A4</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>FULL CETAK (PRINT)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>FULL CETAK (PRINT)</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>Format resmi dengan Kop Surat &amp; Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Terima Barang Fisik &amp; Goods Receipt (GR)</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>FULL AKSES (CREATE)</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>Verifikasi fisik kargo tiba di gudang</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>AI Delivery Order (DO) Scanner</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>FULL AKSES (AI SCAN)</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>Membaca nomor surat jalan &amp; segel paket</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Cetak Slip Bukti Penerimaan Barang (GR)</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Read Only</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>FULL CETAK (PRINT)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>FULL CETAK (PRINT)</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>Berita Acara tanda terima kargo gudang</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Dashboard Dinamis Khusus Role</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>KPI Pemohon</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>KPI Otorisasi</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>KPI Sourcing &amp; PO</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>KPI Logistik &amp; GR</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Global Enterprise KPI</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>Tampilan menyesuaikan peran yang login</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Manajemen Pengguna &amp; Database Seeder</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>Tidak Ada Akses</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>FULL KONTROL ADMIN</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Pengaturan sistem dan keamanan data</t>
         </is>
       </c>
     </row>
@@ -1904,4 +3205,341 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>RINGKASAN SPESIFIKASI TEKNIS &amp; BATASAN RUANG LINGKUP SISTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Take Home Programming Test Software Engineer — Cineul Technologies</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="10" customHeight="1"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Ketentuan Lembar Soal</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Implementasi Nyata pada Aplikasi</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Kesesuaian</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Catatan Teknis Arsitektur</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Pilihan Aplikasi</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Memilih 1 dari 2 (Helpdesk / Procurement)</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Aplikasi Procurement (Pengadaan Terpadu)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>100% Sesuai</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Menangani alur end-to-end pengadaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Bahasa Pemrograman</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Wajib menggunakan Python</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Python 3.9+ &amp; Framework Flask 3.x</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>100% Sesuai</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>Kode bersih, modular &amp; standar PEP 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Basis Data</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Database sqlite / PostgreSQL</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>SQLite Relasional (ACID Compliant)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>100% Sesuai</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Integrasi ketat PRAGMA foreign_keys = ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Batasan Lingkup (In-Scope)</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Request sampai barang/jasa sampai di gudang</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>PR -&gt; Approval -&gt; PO -&gt; Goods Receipt (GR)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>100% Sesuai</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Titik akhir adalah tanda terima fisik di gudang</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Batasan Lingkup (Out-of-Scope)</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Bukan aplikasi gudang internal</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Tidak mengelola bin slotting &amp; kartu stok internal</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>100% Sesuai</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Sesuai batasan tegas spesifikasi soal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Batasan Lingkup (Out-of-Scope)</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Bukan aplikasi pembayaran</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Tidak ada modul disbursement/kas/bank</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>100% Sesuai</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Sesuai batasan tegas spesifikasi soal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Soal 1a: BPMN Swimlane</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Swimlane BPMN, role &gt; 2, direkomendasikan draw.io</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Draw.io Vertikal 5 Roles (SOAL_1A_BPMN_SWIMLANE.drawio)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>100% Selesai</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Alur vertikal panjang ke bawah &amp; siap export PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Soal 1b: WBS Modul &amp; Fitur</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Work Breakdown Structure dalam file Excel</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Excel Multi-Sheet (SOAL_1B_WBS_PROCUREMENT.xlsx)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>100% Selesai</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Lengkap dengan WBS, Matriks RBAC &amp; Spek</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Fitur Opsional (Nilai Plus)</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Salah satu tahapan menggunakan Computer Vision/AI</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>AI Vision Suite di 3 Tahapan (PR, PO, GR)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Melampaui Target</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Semua role merasakan manfaat nyata AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Format Cetak Dokumen</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Dokumen transaksi resmi pengadaan</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Standar Cetak A4, Kop Surat, Stempel Digital, 3 Tanda Tangan</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Standar Industri</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Dokumen PO dan GR siap audit legal</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>